--- a/sheet-template/gameshow-template.xlsx
+++ b/sheet-template/gameshow-template.xlsx
@@ -178,7 +178,7 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Link ảnh đội (tùy chọn). Trống thì dùng chữ viết tắt tên đội.</t>
+        <t>Tên file ảnh đội trong thư mục images/ (vd: doi-01.jpg). Trống thì dùng chữ viết tắt tên đội.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -198,12 +198,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Tên gói câu hỏi. Mỗi gói = 1 câu hỏi (1 dòng).</t>
+        <t>Tên gói câu hỏi. Mỗi gói = 1 câu hỏi (1 dòng). Bắt buộc.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Mã đội sở hữu gói (tùy chọn). Trống = gói chung, đội nào chọn trước thì khóa với đội khác.</t>
+        <t>Mã đội sở hữu gói (vd: doi-01). Bắt buộc.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -213,20 +213,15 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Đáp án (tùy chọn, không hiện trên màn hình).</t>
+        <t>Tên file ảnh minh họa trong thư mục images/ (tùy chọn).</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Link ảnh minh họa (tùy chọn).</t>
+        <t>Thời gian trả lời (giây). Trống = dùng round1_time_seconds trong tab config.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Thời gian trả lời (giây). Trống = dùng round1_time_seconds trong tab config.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Điểm của câu hỏi. Trống = dùng giá trị mặc định trong config.</t>
       </text>
@@ -253,20 +248,15 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Đáp án (tùy chọn).</t>
+        <t>Tên file ảnh minh họa trong thư mục images/ (tùy chọn).</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Link ảnh minh họa (tùy chọn).</t>
+        <t>Thời gian trả lời (giây). Trống = dùng round3_time_seconds trong config.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Thời gian trả lời (giây). Trống = dùng round3_time_seconds trong config.</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Điểm của ô. Trống = dùng giá trị mặc định trong config.</t>
       </text>
@@ -937,16 +927,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -967,20 +956,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>image_url</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>image_url</t>
+          <t>time_seconds</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>time_seconds</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>points</t>
         </is>
@@ -1002,16 +986,11 @@
           <t>Kinh đô của nhà nước Văn Lang được đặt tại vùng đất thuộc tỉnh nào của Việt Nam hiện nay?</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Phú Thọ</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F2" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1031,16 +1010,11 @@
           <t>Nguyên tố hóa học nào chiếm tỷ lệ thể tích lớn nhất trong khí quyển Trái Đất?</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Nitơ (khoảng 78%)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F3" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G3" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1060,16 +1034,11 @@
           <t>Tác phẩm "Truyện Kiều" của đại thi hào Nguyễn Du được viết theo thể thơ nào?</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Thể thơ lục bát</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F4" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G4" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1089,16 +1058,11 @@
           <t>Ánh sáng từ Mặt Trời mất khoảng bao nhiêu phút để truyền tới Trái Đất?</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Khoảng 8 phút 20 giây</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F5" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1118,16 +1082,11 @@
           <t>Sông Mê Kông chảy vào lãnh thổ Việt Nam qua hai nhánh chính là sông Tiền và sông gì?</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Sông Hậu</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F6" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1147,16 +1106,11 @@
           <t>Từ viết tắt "CPU" trong máy tính có nghĩa tiếng Việt là gì?</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Bộ xử lý trung tâm</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F7" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G7" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1176,16 +1130,11 @@
           <t>Quần thể di tích Cố đô Huế được UNESCO công nhận là Di sản Văn hóa Thế giới vào năm nào?</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Năm 1993</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F8" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1205,16 +1154,11 @@
           <t>Quá trình cây xanh tổng hợp chất hữu cơ nhờ năng lượng ánh sáng gọi là gì?</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Quang hợp</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F9" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1234,16 +1178,11 @@
           <t>Vị vua nào đã ban "Chiếu dời đô" đưa kinh đô từ Hoa Lư về Đại La (Thăng Long) năm 1010?</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Lý Thái Tổ (Lý Công Uẩn)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F10" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G10" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1263,16 +1202,11 @@
           <t>Đại dương nào có diện tích và độ sâu lớn nhất thế giới?</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Thái Bình Dương</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F11" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G11" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1292,16 +1226,11 @@
           <t>Lễ hội Đền Hùng tưởng nhớ các Vua Hùng diễn ra vào ngày nào âm lịch hằng năm?</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Mùng 10 tháng 3 âm lịch</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F12" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1321,366 +1250,299 @@
           <t>Trong bảng tuần hoàn hóa học, nguyên tố Vàng có ký hiệu là gì?</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F13" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G13" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 01</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr"/>
+          <t>Gói A</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>doi-07</t>
+        </is>
+      </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Tác giả của bản "Tuyên ngôn Độc lập" khai sinh nước Việt Nam Dân chủ Cộng hòa ngày 2/9/1945 là ai?</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Chủ tịch Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F14" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 02</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
+          <t>Gói B</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>doi-07</t>
+        </is>
+      </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Chiến dịch Hồ Chí Minh lịch sử toàn thắng vào ngày tháng năm nào?</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>30/04/1975</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F15" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 03</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
+          <t>Gói A</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>doi-08</t>
+        </is>
+      </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Trường đại học đầu tiên của Việt Nam tại kinh thành Thăng Long có tên là gì?</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Quốc Tử Giám</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G16" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 04</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr"/>
+          <t>Gói B</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>doi-08</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Trên sông Bạch Đằng năm 938, vị anh hùng nào đã đánh tan quân Nam Hán?</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Ngô Quyền</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G17" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 05</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr"/>
+          <t>Gói A</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>doi-09</t>
+        </is>
+      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Ai là vị trạng nguyên trẻ tuổi nhất trong lịch sử khoa bảng phong kiến Việt Nam?</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Nguyễn Hiền</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 06</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr"/>
+          <t>Gói B</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>doi-09</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Bài hát "Tiến quân ca" - Quốc ca Việt Nam do nhạc sĩ nào sáng tác?</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Văn Cao</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G19" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 07</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr"/>
+          <t>Gói A</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>doi-10</t>
+        </is>
+      </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Đảo lớn nhất của Việt Nam tính theo diện tích là đảo nào?</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Đảo Phú Quốc</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F20" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G20" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 08</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr"/>
+          <t>Gói B</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>doi-10</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Nhà Trần đã ba lần đánh thắng quân xâm lược Nguyên - Mông vào thế kỷ thứ mấy?</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Thế kỷ XIII</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F21" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G21" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 09</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr"/>
+          <t>Gói A</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>doi-11</t>
+        </is>
+      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Chợ nổi Cái Răng là nét văn hóa đặc sắc của thành phố trực thuộc trung ương nào?</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Thành phố Cần Thơ</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F22" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G22" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 10</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr"/>
+          <t>Gói B</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>doi-11</t>
+        </is>
+      </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Cao nguyên đá Đồng Văn nằm ở tỉnh nào của nước ta?</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Tỉnh Hà Giang</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F23" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G23" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 11</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr"/>
+          <t>Gói A</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>doi-12</t>
+        </is>
+      </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Ai là tác giả của "Bình Ngô đại cáo" - bản tuyên ngôn độc lập thứ hai của dân tộc?</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Nguyễn Trãi</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F24" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G24" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Gói Chung 12</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr"/>
+          <t>Gói B</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>doi-12</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Bài thơ thần "Nam quốc sơn hà" tương truyền vang lên bên dòng sông nào?</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sông Như Nguyệt</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F25" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Gói Chung 13</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Hồ nước ngọt tự nhiên lớn nhất miền núi phía Bắc Việt Nam là hồ nào?</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Hồ Ba Bể</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Gói Chung 14</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Đèo Hải Vân nằm giữa ranh giới tỉnh Thừa Thiên Huế và thành phố nào?</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Thành phố Đà Nẵng</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G27" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1696,15 +1558,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1720,20 +1581,15 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>image_url</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>image_url</t>
+          <t>time_seconds</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>time_seconds</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>points</t>
         </is>
@@ -1748,16 +1604,11 @@
           <t>Nhà nước đầu tiên trong lịch sử dân tộc Việt Nam có tên gọi là gì?</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Nhà nước Văn Lang</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E2" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1770,16 +1621,11 @@
           <t>Sông nào dài nhất trên thế giới chảy qua khu vực Đông Bắc châu Phi?</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Sông Nin (Nile)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E3" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1792,16 +1638,11 @@
           <t>Nguyên tố hóa học nào có số hiệu nguyên tử bằng 1 trong bảng tuần hoàn?</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Hiđrô (H)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1814,16 +1655,11 @@
           <t>Tác phẩm "Nhật ký trong tù" của Chủ tịch Hồ Chí Minh được viết bằng chữ gì?</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Chữ Hán</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E5" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1836,16 +1672,11 @@
           <t>Thành phố nào là thủ đô của nước Cộng hòa Nhân dân Trung Hoa?</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Bắc Kinh</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1858,16 +1689,11 @@
           <t>Trong hình học phẳng, đường thẳng đi qua tâm và nối hai điểm trên đường tròn gọi là gì?</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Đường kính</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E7" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F7" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1880,16 +1706,11 @@
           <t>Vịnh biển nào của Việt Nam từng hai lần được UNESCO công nhận là Di sản Thiên nhiên Thế giới về giá trị thẩm mỹ và địa chất?</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Vịnh Hạ Long</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E8" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1902,16 +1723,11 @@
           <t>Ai là người chỉ huy quân dân nhà Trần lập chiến công trên sông Bạch Đằng năm 1288?</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Trần Hưng Đạo (Hưng Đạo Đại Vương Trần Quốc Tuấn)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1924,16 +1740,11 @@
           <t>Hành tinh nào trong Hệ Mặt Trời nổi tiếng với hệ thống vành đai băng và bụi rộng lớn dễ quan sát nhất?</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Sao Thổ (Thổ tinh)</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E10" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F10" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1946,16 +1757,11 @@
           <t>Cơ quan hô hấp chính của loài cá sống dưới nước là bộ phận nào?</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Mang</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E11" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F11" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1968,16 +1774,11 @@
           <t>Tỉnh nào của Việt Nam có diện tích tự nhiên lớn nhất cả nước?</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E12" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F12" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1990,16 +1791,11 @@
           <t>Bản giao hưởng "Định mệnh" (Số 5) là kiệt tác của nhà soạn nhạc người Đức nào?</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Ludwig van Beethoven</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E13" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2012,16 +1808,11 @@
           <t>Đơn vị đo tần số dao động trong hệ đo lường quốc tế SI là gì?</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Héc (Hz - Hertz)</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E14" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F14" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2034,16 +1825,11 @@
           <t>Chiến dịch Điện Biên Phủ năm 1954 kéo dài trong bao nhiêu ngày đêm?</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>56 ngày đêm</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E15" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F15" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2056,16 +1842,11 @@
           <t>Quốc gia nào có diện tích lãnh thổ lớn nhất thế giới?</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Liên bang Nga</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E16" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F16" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2078,16 +1859,11 @@
           <t>Tác giả của truyện ngắn "Vợ nhặt" trong văn học Việt Nam hiện đại là ai?</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Kim Lân</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E17" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F17" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2100,16 +1876,11 @@
           <t>Kim loại nào nhẹ nhất (có khối lượng riêng nhỏ nhất) trong tất cả các kim loại ở điều kiện chuẩn?</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Liti (Li)</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E18" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F18" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2122,16 +1893,11 @@
           <t>Đường xích đạo chia quả địa cầu thành hai phần bằng nhau gọi là gì?</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Bán cầu Bắc và Bán cầu Nam</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E19" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F19" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2144,16 +1910,11 @@
           <t>Kinh thành Huế được xây dựng bắt đầu từ triều vua nào của nhà Nguyễn?</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Vua Gia Long</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E20" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2166,16 +1927,11 @@
           <t>Trong công nghệ thông tin, thuật ngữ "RAM" là viết tắt của cụm từ tiếng Anh nào?</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Random Access Memory (Bộ nhớ truy cập ngẫu nhiên)</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F21" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2188,16 +1944,11 @@
           <t>Loài cây nào thường được xem là biểu tượng cho phẩm chất thanh cao, được đề cử là Quốc hoa Việt Nam?</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Hoa sen</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E22" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F22" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2210,16 +1961,11 @@
           <t>Ai là nhà bác học vĩ đại đã phát hiện ra định luật vạn vật hấp dẫn?</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Isaac Newton</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E23" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F23" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2232,16 +1978,11 @@
           <t>Thành cổ Quảng Trị gắn liền với cuộc chiến đấu 81 ngày đêm mùa hè đỏ lửa vào năm nào?</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Năm 1972</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E24" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F24" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2254,16 +1995,11 @@
           <t>Hồ nước ngọt sâu nhất trên thế giới nằm ở vùng Siberia (Nga) có tên là gì?</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Hồ Baikal</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E25" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F25" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2276,16 +2012,11 @@
           <t>Vitamin nào đóng vai trò quan trọng giúp tăng cường thị lực và phòng ngừa bệnh quáng gà?</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Vitamin A</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E26" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2298,16 +2029,11 @@
           <t>Tác phẩm "Số đỏ" với nhân vật Xuân Tóc Đỏ là tiểu thuyết trào phúng của nhà văn nào?</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Vũ Trọng Phụng</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E27" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F27" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2320,16 +2046,11 @@
           <t>Dãy núi Himalaya nằm ở châu lục nào?</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Châu Á</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F28" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2342,16 +2063,11 @@
           <t>Trong vật lý, đại lượng đặc trưng cho sự nhanh hay chậm của chuyển động gọi là gì?</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Vận tốc (hoặc tốc độ)</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E29" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F29" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2364,16 +2080,11 @@
           <t>Ai là nữ tướng đầu tiên của Quân đội Nhân dân Việt Nam?</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Định</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E30" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F30" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2386,16 +2097,11 @@
           <t>Quần đảo Hoàng Sa trực thuộc đơn vị hành chính cấp tỉnh/thành phố nào của Việt Nam?</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Thành phố Đà Nẵng</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E31" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F31" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2408,16 +2114,11 @@
           <t>Chất khí nào gây ra hiệu ứng nhà kính mạnh mẽ nhất do hoạt động đốt nhiên liệu hóa thạch của con người?</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Khí Cacbon đioxit (CO2)</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E32" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F32" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2430,16 +2131,11 @@
           <t>Bài thơ "Đất Nước" (trích trường ca Mặt đường khát vọng) là sáng tác của nhà thơ nào?</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Nguyễn Khoa Điềm</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E33" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F33" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2452,16 +2148,11 @@
           <t>Eo biển nào ngăn cách đảo Anh với lục địa châu Âu?</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Eo biển Manche (English Channel)</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E34" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F34" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2474,16 +2165,11 @@
           <t>Một byte trong tin học tương đương với bao nhiêu bit?</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>8 bit</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E35" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F35" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2496,16 +2182,11 @@
           <t>Phong trào Cần Vương cuối thế kỷ XIX được phát động bởi chiếu Cần Vương nhân danh vị vua nào?</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Vua Hàm Nghi</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E36" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F36" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2518,16 +2199,11 @@
           <t>Nhóm máu nào được gọi là nhóm máu "chuyên cho" (hồng cầu lắng) trong truyền máu cổ điển?</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Nhóm máu O (O Rh-)</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F37" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2540,16 +2216,11 @@
           <t>Sông Hồng chảy vào địa phận Việt Nam đầu tiên tại tỉnh nào?</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Tỉnh Lào Cai</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E38" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F38" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2562,16 +2233,11 @@
           <t>Tác giả của thuyết tương đối rộng và thuyết tương đối hẹp trong vật lý hiện đại là ai?</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Albert Einstein</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E39" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F39" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2584,16 +2250,11 @@
           <t>Di sản Văn hóa Thế giới Phố cổ Hội An nằm bên bờ con sông nào?</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Sông Thu Bồn (nhánh sông Hoài)</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E40" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F40" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2606,16 +2267,11 @@
           <t>Hợp kim đồng thau là sự kết hợp chủ yếu giữa kim loại đồng (Cu) và kim loại nào?</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Kẽm (Zn)</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="E41" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F41" s="4" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2628,16 +2284,11 @@
           <t>Hiệp định Genève về chấm dứt chiến tranh, lập lại hòa bình ở Đông Dương được ký kết vào năm nào?</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Năm 1954</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E42" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F42" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2650,16 +2301,11 @@
           <t>Châu lục nào nằm hoàn toàn ở bán cầu Nam và được bao phủ bởi băng tuyết quanh năm?</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Châu Nam Cực</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E43" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F43" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2672,16 +2318,11 @@
           <t>Nhà bác học Marie Curie đã tìm ra hai nguyên tố phóng xạ nào?</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Poloni (Po) và Rađi (Ra)</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr"/>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="E44" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F44" s="4" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2694,16 +2335,11 @@
           <t>Trong văn học dân gian Việt Nam, vị thần nào trong "Tứ bất tử" gắn với truyền thuyết chống lũ lụt sông Hồng?</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Sơn Tinh (Tản Viên Sơn Thánh)</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E45" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F45" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2716,16 +2352,11 @@
           <t>Ký hiệu hóa học của nguyên tố Sắt trong bảng tuần hoàn là gì?</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Fe</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr"/>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E46" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F46" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2738,16 +2369,11 @@
           <t>Hiệp hội các quốc gia Đông Nam Á (ASEAN) được thành lập vào năm nào?</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Năm 1967</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="E47" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F47" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2760,16 +2386,11 @@
           <t>Đỉnh núi cao nhất trên Trái Đất thuộc dãy Himalaya có tên là gì?</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Đỉnh Everest (Chomolungma)</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr"/>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E48" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F48" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2782,16 +2403,11 @@
           <t>Ai là người Việt Nam đầu tiên bay vào vũ trụ trên tàu Liên hợp 37 năm 1980?</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Phạm Tuân</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E49" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F49" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2804,16 +2420,11 @@
           <t>Trong toán học, hằng số Pi (tỷ số giữa chu vi và đường kính đường tròn) có giá trị xấp xỉ hai chữ số thập phân là bao nhiêu?</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>3,14</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E50" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F50" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2826,16 +2437,11 @@
           <t>Bến Nhà Rồng - nơi người thanh niên Nguyễn Tất Thành ra đi tìm đường cứu nước năm 1911 - nằm tại thành phố nào hiện nay?</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E51" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F51" s="4" t="n">
         <v>30</v>
       </c>
     </row>

--- a/sheet-template/gameshow-template.xlsx
+++ b/sheet-template/gameshow-template.xlsx
@@ -10,9 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="huong_dan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teams" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="round1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="round3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="round2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="round3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="judges" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -198,7 +199,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Tên gói câu hỏi. Mỗi gói = 1 câu hỏi (1 dòng). Bắt buộc.</t>
+        <t>Tên gói chủ đề (mỗi gói = 1 câu hỏi/chủ đề). Bắt buộc.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -208,7 +209,7 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Nội dung câu hỏi. Bắt buộc.</t>
+        <t>Nội dung chủ đề tự giới thiệu / thuyết trình. Bắt buộc.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -218,12 +219,12 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Thời gian trả lời (giây). Trống = dùng round1_time_seconds trong tab config.</t>
+        <t>Thời gian tối đa (giây). Trống = dùng round1_time_seconds trong config.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Điểm của câu hỏi. Trống = dùng giá trị mặc định trong config.</t>
+        <t>Điểm tối đa của phần thi. Trống = dùng round1_default_points.</t>
       </text>
     </comment>
   </commentList>
@@ -238,12 +239,72 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Số ô trên bảng (1-50). Bắt buộc, không trùng.</t>
+        <t>Mã bộ đề (vd: 1, 2...). Bắt buộc.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Nội dung câu hỏi. Bắt buộc.</t>
+        <t>Số thứ tự câu hỏi trong bộ đề (1-10). Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Nội dung câu hỏi trắc nghiệm. Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Nội dung đáp án A. Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Nội dung đáp án B. Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Nội dung đáp án C. Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Nội dung đáp án D. Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Đáp án đúng (A, B, C hoặc D). Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Thời gian trả lời (giây). Trống = dùng round2_time_seconds trong config.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Tên file ảnh minh họa trong thư mục images/ (tùy chọn).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Mẫu</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Số ô tình huống trên bảng (1-15). Bắt buộc, không trùng.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Nội dung tình huống nghiệp vụ PCCC và CNCH. Bắt buộc.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -258,27 +319,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Điểm của ô. Trống = dùng giá trị mặc định trong config.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Mẫu</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Tên cài đặt. Không đổi tên cột key.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Giá trị. Sửa cột này để đổi tên hội thi, thời gian, màu sắc...</t>
+        <t>Điểm tối đa của ô. Trống = dùng round3_default_points trong config.</t>
       </text>
     </comment>
   </commentList>
@@ -293,7 +334,32 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Mã đội. Tab này do web tự ghi qua Apps Script; có thể để trống.</t>
+        <t>Mã giám khảo, duy nhất (vd: gk-01). Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Họ tên hoặc danh xưng giám khảo. Bắt buộc.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Mẫu</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Tên cài đặt (key). Không đổi tên cột key.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Giá trị cài đặt (tên hội thi, thời gian, điểm tối đa, mật khẩu sha256...).</t>
       </text>
     </comment>
   </commentList>
@@ -598,7 +664,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HƯỚNG DẪN SỬ DỤNG FILE MẪU</t>
+          <t>HƯỚNG DẪN SỬ DỤNG FILE MẪU HỘI THI PCCC VÀ CNCH</t>
         </is>
       </c>
     </row>
@@ -615,35 +681,35 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2. Giữ nguyên TÊN CÁC TAB (teams, round1, round3, config, scores) và TÊN CỘT ở dòng 1 (ô màu cam).</t>
+          <t>2. Giữ nguyên TÊN CÁC TAB (teams, round1, round2, round3, judges, config) và TÊN CỘT ở dòng 1 (ô màu cam).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3. Sửa dữ liệu từ dòng 2 trở đi. Rê chuột vào tiêu đề cột để xem ghi chú từng cột.</t>
+          <t>3. Sửa dữ liệu từ dòng 2 trở đi. Rê chuột vào tiêu đề cột để xem ghi chú hướng dẫn từng cột.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>4. Chia sẻ &gt; Bất kỳ ai có đường liên kết &gt; Người xem. Copy link, dán vào mục Cài đặt ở thanh bên trái trên web.</t>
+          <t>4. Chia sẻ sheet: Bất kỳ ai có đường liên kết &gt; Người xem. Copy link, dán vào mục Cài đặt trên màn hình Dẫn chương trình.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>5. (Tùy chọn) Ghi điểm từ web vào tab scores: làm theo README, phần Apps Script.</t>
+          <t>5. Điểm số và trạng thái trận đấu được đồng bộ thời gian thực qua Firebase Realtime Database.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6. Sửa sheet xong, bấm 'Tải lại dữ liệu' trên web để cập nhật.</t>
+          <t>6. Sửa sheet xong, bấm 'Tải lại dữ liệu' trên web để cập nhật toàn bộ thiết bị.</t>
         </is>
       </c>
     </row>
@@ -653,7 +719,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Dữ liệu trong các tab là ví dụ, thay bằng đội và câu hỏi thật. Tab này (huong_dan) có thể xóa.</t>
+          <t>Dữ liệu trong các tab là ví dụ mẫu cho 12 đội, 3 giám khảo, 2 bộ đề trắc nghiệm Vòng 2 và 15 tình huống Vòng 3.</t>
         </is>
       </c>
     </row>
@@ -983,15 +1049,15 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Kinh đô của nhà nước Văn Lang được đặt tại vùng đất thuộc tỉnh nào của Việt Nam hiện nay?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Nhà chung cư cao tầng và khu căn hộ hỗn hợp</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr"/>
       <c r="E2" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1007,15 +1073,15 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Nguyên tố hóa học nào chiếm tỷ lệ thể tích lớn nhất trong khí quyển Trái Đất?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Chợ truyền thống và trung tâm thương mại</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -1031,15 +1097,15 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Tác phẩm "Truyện Kiều" của đại thi hào Nguyễn Du được viết theo thể thơ nào?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Nhà ở kết hợp sản xuất, kinh doanh (nhà ống liền kề)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1055,15 +1121,15 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Ánh sáng từ Mặt Trời mất khoảng bao nhiêu phút để truyền tới Trái Đất?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Cơ sở sản xuất công nghiệp, kho tàng trong khu công nghiệp</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -1079,15 +1145,15 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Sông Mê Kông chảy vào lãnh thổ Việt Nam qua hai nhánh chính là sông Tiền và sông gì?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Bệnh viện và các cơ sở khám chữa bệnh</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -1101,17 +1167,17 @@
           <t>doi-03</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Từ viết tắt "CPU" trong máy tính có nghĩa tiếng Việt là gì?</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Trường học và các cơ sở giáo dục đào tạo</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1127,15 +1193,15 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Quần thể di tích Cố đô Huế được UNESCO công nhận là Di sản Văn hóa Thế giới vào năm nào?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Cơ sở kinh doanh dịch vụ karaoke, vũ trường, quán bar</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1151,15 +1217,15 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Quá trình cây xanh tổng hợp chất hữu cơ nhờ năng lượng ánh sáng gọi là gì?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Cửa hàng kinh doanh xăng dầu và khí đốt hóa lỏng (LPG)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1175,15 +1241,15 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Vị vua nào đã ban "Chiếu dời đô" đưa kinh đô từ Hoa Lư về Đại La (Thăng Long) năm 1010?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Khu dân cư đô thị có ngõ sâu, hẹp và làng nghề truyền thống</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1197,17 +1263,17 @@
           <t>doi-05</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Đại dương nào có diện tích và độ sâu lớn nhất thế giới?</t>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Tuyên truyền an toàn PCCC và CNCH trong sử dụng điện sinh hoạt, sạc xe đạp điện và xe máy điện</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -1223,15 +1289,15 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Lễ hội Đền Hùng tưởng nhớ các Vua Hùng diễn ra vào ngày nào âm lịch hằng năm?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Tòa nhà văn phòng làm việc và trụ sở cơ quan</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -1247,15 +1313,15 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Trong bảng tuần hoàn hóa học, nguyên tố Vàng có ký hiệu là gì?</t>
+          <t>Tuyên truyền an toàn PCCC và CNCH tại Rừng phòng hộ, vườn quốc gia và khu bảo tồn thiên nhiên</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1271,15 +1337,15 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Tác giả của bản "Tuyên ngôn Độc lập" khai sinh nước Việt Nam Dân chủ Cộng hòa ngày 2/9/1945 là ai?</t>
+          <t>Tuyên truyền kỹ năng tự thoát nạn và cứu nạn khi xảy ra cháy tại công trình ngầm và tầng hầm</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -1295,15 +1361,15 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Chiến dịch Hồ Chí Minh lịch sử toàn thắng vào ngày tháng năm nào?</t>
+          <t>Tuyên truyền xây dựng và nhân rộng mô hình "Tổ liên gia an toàn PCCC" và Điểm chữa cháy công cộng</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1319,15 +1385,15 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Trường đại học đầu tiên của Việt Nam tại kinh thành Thăng Long có tên là gì?</t>
+          <t>Tuyên truyền kỹ năng sử dụng bình chữa cháy xách tay và phương tiện cứu nạn ban đầu cho người dân</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1343,15 +1409,15 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Trên sông Bạch Đằng năm 938, vị anh hùng nào đã đánh tan quân Nam Hán?</t>
+          <t>Tuyên truyền an toàn PCCC trong thi công cải tạo, sửa chữa có hoạt động hàn cắt kim loại tại cơ sở</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1367,15 +1433,15 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Ai là vị trạng nguyên trẻ tuổi nhất trong lịch sử khoa bảng phong kiến Việt Nam?</t>
+          <t>Tuyên truyền an toàn PCCC và kỹ năng thoát nạn tại Khách sạn và các cơ sở lưu trú du lịch</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1391,15 +1457,15 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Bài hát "Tiến quân ca" - Quốc ca Việt Nam do nhạc sĩ nào sáng tác?</t>
+          <t>Tuyên truyền an toàn PCCC trong bảo quản, vận chuyển và sử dụng hóa chất nguy hiểm cháy, nổ</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -1413,17 +1479,17 @@
           <t>doi-10</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Đảo lớn nhất của Việt Nam tính theo diện tích là đảo nào?</t>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Tuyên truyền kỹ năng an toàn PCCC trong dịp Tết Nguyên đán, lễ hội và việc thắp hương thờ cúng</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1439,15 +1505,15 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Nhà Trần đã ba lần đánh thắng quân xâm lược Nguyên - Mông vào thế kỷ thứ mấy?</t>
+          <t>Tuyên truyền hướng dẫn cài đặt và sử dụng ứng dụng "Báo cháy 114" hỗ trợ cứu nạn cứu hộ</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -1463,15 +1529,15 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Chợ nổi Cái Răng là nét văn hóa đặc sắc của thành phố trực thuộc trung ương nào?</t>
+          <t>Tuyên truyền an toàn PCCC tại Cơ sở chế biến gỗ, may mặc và sản xuất vật liệu dễ bắt cháy</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -1485,17 +1551,17 @@
           <t>doi-11</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Cao nguyên đá Đồng Văn nằm ở tỉnh nào của nước ta?</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Tuyên truyền giải pháp mở lối thoát nạn khẩn cấp thứ hai đối với nhà ở có chuồng cọp lồng sắt</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -1511,15 +1577,15 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Ai là tác giả của "Bình Ngô đại cáo" - bản tuyên ngôn độc lập thứ hai của dân tộc?</t>
+          <t>Tuyên truyền vận động người dân tự trang bị bình cứu hỏa, búa thoát hiểm và mặt nạ lọc độc</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -1535,15 +1601,15 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Bài thơ thần "Nam quốc sơn hà" tương truyền vang lên bên dòng sông nào?</t>
+          <t>Tuyên truyền vai trò, trách nhiệm của người đứng đầu cơ quan, doanh nghiệp về công tác PCCC và CNCH</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="n">
-        <v>15</v>
+        <v>900</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1558,892 +1624,952 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>option_c</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>option_d</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>time_seconds</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>image_url</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>time_seconds</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Nhà nước đầu tiên trong lịch sử dân tộc Việt Nam có tên gọi là gì?</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Số điện thoại khẩn cấp gọi lực lượng Cảnh sát PCCC và CNCH tại Việt Nam là gì?</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Sông nào dài nhất trên thế giới chảy qua khu vực Đông Bắc châu Phi?</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Bình chữa cháy bột MFZ4 chứa chất chữa cháy chính ở dạng nào?</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Dạng khí hóa lỏng</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Dạng bọt hóa học</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Dạng bột khô</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Dạng dung dịch nước</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Nguyên tố hóa học nào có số hiệu nguyên tử bằng 1 trong bảng tuần hoàn?</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Khi phát hiện đám cháy trong phòng kín có nhiều khói độc người thoát nạn cần di chuyển như thế nào?</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Chạy thẳng đứng thật nhanh</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Bò hoặc khom thấp người, dùng khăn ướt bịt mũi miệng</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Nhảy qua cửa sổ ngay lập tức</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Nấp dưới gầm bàn hoặc gầm giường</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Tác phẩm "Nhật ký trong tù" của Chủ tịch Hồ Chí Minh được viết bằng chữ gì?</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Chất chữa cháy nào KHÔNG ĐƯỢC dùng để dập tắt đám cháy kim loại kiềm như Natri hoặc Kali?</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Nước</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Cát khô</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Bột chữa cháy đặc biệt</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Đất khô</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Thành phố nào là thủ đô của nước Cộng hòa Nhân dân Trung Hoa?</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Thiết bị nào sau đây thuộc hệ thống báo cháy tự động?</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Đầu báo khói</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Lăng chữa cháy</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Cuộn vòi chữa cháy</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Trụ nước chữa cháy</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Trong hình học phẳng, đường thẳng đi qua tâm và nối hai điểm trên đường tròn gọi là gì?</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Khi sử dụng bình chữa cháy khí CO2 (MT3 MT5) người sử dụng KHÔNG NÊN cầm vào bộ phận nào để tránh bị bỏng lạnh?</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Quai xách bình</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Cò bóp</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Loa phun và ống dẫn khí</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Chốt hãm an toàn</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Vịnh biển nào của Việt Nam từng hai lần được UNESCO công nhận là Di sản Thiên nhiên Thế giới về giá trị thẩm mỹ và địa chất?</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Nguyên lý chữa cháy bằng cách ngăn cách ôxy trong không khí với bề mặt chất cháy được gọi là gì?</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Phương pháp làm lạnh</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Phương pháp cách ly</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Phương pháp làm loãng</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Phương pháp kìm hãm hóa học</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Ai là người chỉ huy quân dân nhà Trần lập chiến công trên sông Bạch Đằng năm 1288?</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Phương tiện cơ giới chữa cháy chủ yếu của lực lượng Cảnh sát PCCC và CNCH là gì?</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Xe cứu thương</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Xe chữa cháy chuyên dụng</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Xe cẩu cứu hộ</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Xe bọc thép</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Hành tinh nào trong Hệ Mặt Trời nổi tiếng với hệ thống vành đai băng và bụi rộng lớn dễ quan sát nhất?</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Ngày toàn dân phòng cháy và chữa cháy tại Việt Nam là ngày nào hàng năm?</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Ngày 19 tháng 8</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Ngày 02 tháng 9</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Ngày 04 tháng 10</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Ngày 22 tháng 12</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Cơ quan hô hấp chính của loài cá sống dưới nước là bộ phận nào?</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Màu sắc quy chuẩn của biển chỉ dẫn lối thoát nạn (EXIT) theo Tiêu chuẩn Việt Nam là màu gì?</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Chữ trắng nền xanh lá cây</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Chữ vàng nền đỏ</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Chữ đen nền vàng</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Chữ xanh nền trắng</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Tỉnh nào của Việt Nam có diện tích tự nhiên lớn nhất cả nước?</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Luật Phòng cháy và chữa cháy của nước Cộng hòa XHCN Việt Nam được ban hành năm nào?</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Năm 2001</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Năm 2005</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Năm 2010</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Năm 2015</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Bản giao hưởng "Định mệnh" (Số 5) là kiệt tác của nhà soạn nhạc người Đức nào?</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Khí CO2 trong bình chữa cháy dập tắt lửa chủ yếu dựa trên nguyên lý nào?</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Kìm hãm phản ứng hóa học chuỗi</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Làm loãng nồng độ ôxy và làm lạnh bề mặt chất cháy</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Tạo màng bọt bao phủ chất cháy</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Thấm ướt làm mát sâu chất cháy</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Đơn vị đo tần số dao động trong hệ đo lường quốc tế SI là gì?</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Lực lượng nào là lực lượng nòng cốt trong hoạt động PCCC toàn dân ở cơ sở?</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Lực lượng dân phòng và PCCC cơ sở</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Lực lượng Cảnh sát giao thông</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Lực lượng bảo vệ dân phố</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Lực lượng dân quân tự vệ</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Chiến dịch Điện Biên Phủ năm 1954 kéo dài trong bao nhiêu ngày đêm?</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Khi xảy ra cháy ở chung cư cao tầng phương tiện thoát hiểm nào TUYỆT ĐỐI KHÔNG được sử dụng?</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Cầu thang bộ thoát hiểm</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Thang máy thông thường</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Thang dây cứu nạn ngoài ban công</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Ống tụt cứu người</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Quốc gia nào có diện tích lãnh thổ lớn nhất thế giới?</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Đám cháy loại B theo phân loại tiêu chuẩn là đám cháy của các chất nào?</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Chất rắn thông thường</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Chất lỏng và chất rắn hóa lỏng</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Chất khí cháy</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Thiết bị điện đang có điện</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Tác giả của truyện ngắn "Vợ nhặt" trong văn học Việt Nam hiện đại là ai?</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Khoảng cách an toàn tối thiểu khi phun nước chữa cháy vào đám cháy thiết bị điện có điện áp dưới 1kV là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>0.5 mét</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>1.5 mét</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2.5 mét</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>3.5 mét</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Kim loại nào nhẹ nhất (có khối lượng riêng nhỏ nhất) trong tất cả các kim loại ở điều kiện chuẩn?</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>30</v>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Khi cứu người bị ngạt khói trong đám cháy ra nơi an toàn việc đầu tiên cần làm là gì?</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Cho uống nhiều nước ngọt</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Đặt nằm nghiêng, kiểm tra đường thở và hô hấp nhân tạo nếu ngừng thở</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Bôi dầu gió vào thái dương</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Đắp chăn ấm phủ kín đầu</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Đường xích đạo chia quả địa cầu thành hai phần bằng nhau gọi là gì?</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Phương pháp nào sau đây dùng để kiểm tra độ kín của đường ống dẫn khí gas dân dụng an toàn nhất?</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Dùng bật lửa soi</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Dùng nước bọt xà phòng bôi lên mối nối</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Ngửi trực tiếp sát van bình</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Dùng quạt thổi mạnh</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Kinh thành Huế được xây dựng bắt đầu từ triều vua nào của nhà Nguyễn?</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Biện pháp phòng cháy hữu hiệu nhất trong việc sử dụng điện tại hộ gia đình là gì?</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Không ngắt điện khi ra khỏi nhà</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Sử dụng aptomat (CB) phù hợp công suất và ngắt nguồn khi không dùng</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Cắm nhiều thiết bị công suất lớn vào một ổ cắm</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Đấu nối trực tiếp không qua cầu chì</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Trong công nghệ thông tin, thuật ngữ "RAM" là viết tắt của cụm từ tiếng Anh nào?</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Loài cây nào thường được xem là biểu tượng cho phẩm chất thanh cao, được đề cử là Quốc hoa Việt Nam?</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Ai là nhà bác học vĩ đại đã phát hiện ra định luật vạn vật hấp dẫn?</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Thành cổ Quảng Trị gắn liền với cuộc chiến đấu 81 ngày đêm mùa hè đỏ lửa vào năm nào?</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Hồ nước ngọt sâu nhất trên thế giới nằm ở vùng Siberia (Nga) có tên là gì?</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Vitamin nào đóng vai trò quan trọng giúp tăng cường thị lực và phòng ngừa bệnh quáng gà?</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Tác phẩm "Số đỏ" với nhân vật Xuân Tóc Đỏ là tiểu thuyết trào phúng của nhà văn nào?</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Dãy núi Himalaya nằm ở châu lục nào?</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Trong vật lý, đại lượng đặc trưng cho sự nhanh hay chậm của chuyển động gọi là gì?</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Ai là nữ tướng đầu tiên của Quân đội Nhân dân Việt Nam?</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Quần đảo Hoàng Sa trực thuộc đơn vị hành chính cấp tỉnh/thành phố nào của Việt Nam?</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Chất khí nào gây ra hiệu ứng nhà kính mạnh mẽ nhất do hoạt động đốt nhiên liệu hóa thạch của con người?</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Bài thơ "Đất Nước" (trích trường ca Mặt đường khát vọng) là sáng tác của nhà thơ nào?</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Eo biển nào ngăn cách đảo Anh với lục địa châu Âu?</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Một byte trong tin học tương đương với bao nhiêu bit?</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Phong trào Cần Vương cuối thế kỷ XIX được phát động bởi chiếu Cần Vương nhân danh vị vua nào?</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Nhóm máu nào được gọi là nhóm máu "chuyên cho" (hồng cầu lắng) trong truyền máu cổ điển?</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Sông Hồng chảy vào địa phận Việt Nam đầu tiên tại tỉnh nào?</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Tác giả của thuyết tương đối rộng và thuyết tương đối hẹp trong vật lý hiện đại là ai?</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Di sản Văn hóa Thế giới Phố cổ Hội An nằm bên bờ con sông nào?</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Hợp kim đồng thau là sự kết hợp chủ yếu giữa kim loại đồng (Cu) và kim loại nào?</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Hiệp định Genève về chấm dứt chiến tranh, lập lại hòa bình ở Đông Dương được ký kết vào năm nào?</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Châu lục nào nằm hoàn toàn ở bán cầu Nam và được bao phủ bởi băng tuyết quanh năm?</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
-      <c r="D43" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Nhà bác học Marie Curie đã tìm ra hai nguyên tố phóng xạ nào?</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Trong văn học dân gian Việt Nam, vị thần nào trong "Tứ bất tử" gắn với truyền thuyết chống lũ lụt sông Hồng?</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Ký hiệu hóa học của nguyên tố Sắt trong bảng tuần hoàn là gì?</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr"/>
-      <c r="D46" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Hiệp hội các quốc gia Đông Nam Á (ASEAN) được thành lập vào năm nào?</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr"/>
-      <c r="D47" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Đỉnh núi cao nhất trên Trái Đất thuộc dãy Himalaya có tên là gì?</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Ai là người Việt Nam đầu tiên bay vào vũ trụ trên tàu Liên hợp 37 năm 1980?</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr"/>
-      <c r="D49" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Trong toán học, hằng số Pi (tỷ số giữa chu vi và đường kính đường tròn) có giá trị xấp xỉ hai chữ số thập phân là bao nhiêu?</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Bến Nhà Rồng - nơi người thanh niên Nguyễn Tất Thành ra đi tìm đường cứu nước năm 1911 - nằm tại thành phố nào hiện nay?</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>30</v>
-      </c>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Mô hình an toàn PCCC nào đang được triển khai nhân rộng tại các khu dân cư hộ gia đình kết hợp sản xuất kinh doanh?</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Tổ liên gia an toàn PCCC</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Tổ tự quản an ninh trật tự</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Tổ xung kích cứu nạn cứu hộ</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Đội PCCC tình nguyện</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2457,287 +2583,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>number</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>image_url</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>time_seconds</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>points</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>show_title</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Đấu Trường Tri Thức 2026</t>
-        </is>
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống phát hiện rò rỉ khí gas tại bếp ăn tập thể. Đội thi hãy thực hiện bài tuyên truyền hướng dẫn các bước xử lý tại chỗ và cách thức thông báo cho mọi người thoát nạn an toàn?</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>show_subtitle</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Hội thi tìm hiểu kiến thức tổng hợp &amp; bản lĩnh đồng đội</t>
-        </is>
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống cháy tại tầng 3 nhà ở kết hợp kinh doanh quần áo (nhà ống 1 lối thoát nạn) có người mắc kẹt trên tầng tum. Hãy thuyết trình phương án truyền thông kỹ năng cứu nạn và thoát hiểm cho người dân?</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>round1_name</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Vòng 1: Khởi Động</t>
-        </is>
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống xảy ra chập cháy bình ắc quy xe máy điện khi đang sạc tại tầng hầm chung cư mini lúc nửa đêm. Đội thi hãy trình bày bài truyền thông hướng dẫn cư dân xử lý ban đầu và ngăn cháy lan?</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>round1_description</t>
-        </is>
+      <c r="A5" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Mỗi đội lựa chọn 1 trong 2 gói câu hỏi được đề xuất và suy nghĩ trả lời câu hỏi trong thời gian đếm ngược.</t>
-        </is>
+          <t>Tình huống một nhân viên bị bắt lửa vào quần áo và đang hoảng loạn tháo chạy. Đội thi hãy hướng dẫn và tuyên truyền cách xử lý dập lửa trên người nạn nhân cùng biện pháp sơ cấp cứu ban đầu?</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>round2_name</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Vòng 2: Vượt Chướng Ngại Vật</t>
-        </is>
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống kiểm tra an toàn PCCC phát hiện lối thoát nạn khẩn cấp bị khóa xích và chuông báo cháy bị tắt. Cán bộ kiểm tra thực hiện công tác tuyên truyền vận động và xử lý nghiệp vụ đối với cơ sở ra sao?</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>round2_description</t>
-        </is>
+      <c r="A7" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Phần thi tương tác trực tiếp trên sân khấu. Điểm số của từng đội được Ban thư ký cập nhật vào bảng điểm.</t>
-        </is>
+          <t>Tình huống chuông báo cháy chung cư cao tầng kêu lúc rạng sáng cư dân hoảng loạn chen lấn vào thang máy. Hãy thực hiện bài phát thanh tuyên truyền hướng dẫn thoát nạn an toàn và trấn an người dân?</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>round3_name</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Vòng 3: Tăng Tốc &amp; Về Đích</t>
-        </is>
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống xảy ra sự cố cháy xe ô tô chở khách trên đường cao tốc. Đội thi hãy tuyên truyền phổ biến phương án tổ chức sơ tán hành khách và dập lửa ban đầu cho các tài xế?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>round3_description</t>
-        </is>
+      <c r="A9" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bảng 50 ô câu hỏi bí mật với các mức điểm khác nhau. Đội thi chọn ô số và trả lời trong thời gian quy định.</t>
-        </is>
+          <t>Tình huống một nạn nhân bị mắc kẹt chân trong thang cuốn tại trung tâm thương mại đang có khói bốc lên. Đội thi tuyên truyền kỹ năng xử lý tình huống khẩn cấp cho lực lượng cơ sở như thế nào?</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>round1_time_seconds</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống tuyên truyền an toàn PCCC cho các tiểu thương tại chợ truyền thống về việc thắp hương thờ cúng và câu móc điện tùy tiện. Đội thi xây dựng bài thuyết trình thuyết phục hiệu quả ra sao?</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>round3_time_seconds</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống cháy chảo dầu mỡ đang đun nấu trên bếp công nghiệp đầu bếp chuẩn bị dội nước vào dập lửa. Đội thi can thiệp và tuyên truyền hướng dẫn kỹ năng dập tắt an toàn tình huống trên ra sao?</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>round1_default_points</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống căn hộ khóa trái cửa có khói đen đặc bốc ra từ khe cửa và có tiếng trẻ em kêu cứu. Đội thi tuyên truyền kỹ năng cứu người phá dỡ và chữa cháy ban đầu cho người dân xung quanh như thế nào?</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>round3_default_points</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống mưa ngập sâu tầng hầm tòa nhà có nguy cơ rò rỉ điện từ trạm biến áp và máy phát điện. Cán bộ PCCC tuyên truyền phổ biến các biện pháp đảm bảo an toàn cho ban quản lý tòa nhà ra sao?</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>round1_packages_offered</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống tổ chức chữa cháy tại khu dân cư trong ngõ hẻm sâu hơn 200m xe chữa cháy không vào được. Đội thi tuyên truyền giải pháp phát huy mô hình Tổ liên gia an toàn PCCC và Điểm chữa cháy công cộng?</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>warning_seconds</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống đám cháy bao vây nạn nhân tại tầng 2 nhà ống có ban công bị rào chắn chuồng cọp lồng sắt kiên cố. Đội thi tuyên truyền kỹ năng sinh tồn và hướng dẫn người dân cắt lồng sắt mở lối thoát hiểm?</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>theme_mode</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>bg_color</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>#F5F4ED</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>surface_color</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>#FAF9F5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>text_color</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>#141413</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>muted_color</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>#6B6960</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>accent_color</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>#D97757</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>accent_dark_color</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>#C6613F</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>border_color</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>#E3E0D3</t>
-        </is>
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Tình huống xảy ra sự cố cháy tại phòng máy chủ (Server) chứa nhiều thiết bị điện tử quan trọng. Đội thi tuyên truyền hướng dẫn lựa chọn chất chữa cháy và biện pháp dập lửa an toàn phù hợp ra sao?</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2752,246 +2887,475 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>round1</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>round2</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>round3</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>updated_at</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>doi-01</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
+          <t>gk-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Ban Giám khảo 1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>doi-02</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
+          <t>gk-02</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Ban Giám khảo 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>doi-03</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
+          <t>gk-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Ban Giám khảo 3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>show_title</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Hội thi cán bộ tuyên truyền kiểm tra giỏi về PCCC và CNCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>show_subtitle</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Hệ thống thi đấu trực tiếp đa màn hình</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>round1_name</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Phần thi thứ nhất: Tuyên truyền về PCCC và CNCH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>doi-04</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+          <t>round1_description</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Mỗi đội lựa chọn 1 trong 2 cơ sở/chủ đề và thuyết trình tuyên truyền (tối đa 15 phút).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>doi-05</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+          <t>round2_name</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Phần thi thứ hai: Kiến thức pháp luật, nghiệp vụ về PCCC và CNCH</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>doi-06</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+          <t>round2_description</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>10 câu hỏi trắc nghiệm A/B/C/D trên thiết bị iPad; tính điểm chính xác và tốc độ trả lời.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>doi-07</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>round3_name</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Phần thi thứ ba: Xử lý tình huống truyền thông về PCCC và CNCH</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>doi-08</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+          <t>round3_description</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>15 ô tình huống thực tế về PCCC và CNCH (2 phút chuẩn bị + 5 phút trả lời); Ban Giám khảo chấm điểm trên iPad.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>doi-09</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
+          <t>round1_time_seconds</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>doi-10</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
+          <t>round1_default_points</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>doi-11</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
+          <t>round1_max_content</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>doi-12</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
+          <t>round1_max_manner</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>round1_packages_offered</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>round2_time_seconds</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>round2_max_points</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>round2_min_points</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>round2_divisor</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>round3_time_seconds</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>round3_default_points</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>round3_max_content</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>round3_max_manner</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>warning_seconds</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>password_host_sha256</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>password_judge_sha256</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>password_team_sha256</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>theme_mode</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>bg_color</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>#F5F4ED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>surface_color</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>#FAF9F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>text_color</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>#141413</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>muted_color</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>#6B6960</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>accent_color</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>#D97757</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>accent_dark_color</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>#C6613F</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>border_color</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>#E3E0D3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sheet-template/gameshow-template.xlsx
+++ b/sheet-template/gameshow-template.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="round2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="round3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="judges" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="accounts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -354,12 +355,47 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>Tên đăng nhập (không phân biệt hoa thường). Bắt buộc, duy nhất.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Mật khẩu đăng nhập (văn bản thuần). Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Vai trò: host (dẫn chương trình), judge (giám khảo), hoặc team (đội thi). Bắt buộc.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Mã giám khảo (từ tab judges) hoặc mã đội (từ tab teams). Để trống với host.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Tên hiển thị người dùng (tùy chọn).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Mẫu</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
         <t>Tên cài đặt (key). Không đổi tên cột key.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Giá trị cài đặt (tên hội thi, thời gian, điểm tối đa, mật khẩu sha256...).</t>
+        <t>Giá trị cài đặt (tên hội thi, thời gian, điểm tối đa, màu giao diện...).</t>
       </text>
     </comment>
   </commentList>
@@ -681,7 +717,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2. Giữ nguyên TÊN CÁC TAB (teams, round1, round2, round3, judges, config) và TÊN CỘT ở dòng 1 (ô màu cam).</t>
+          <t>2. Giữ nguyên TÊN CÁC TAB (teams, round1, round2, round3, judges, accounts, config) và TÊN CỘT ở dòng 1 (ô màu cam).</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2990,484 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>ref_id</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Dẫn chương trình</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>gk1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>judge</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>gk-01</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Ban Giám khảo 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>gk2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>judge</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>gk-02</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Ban Giám khảo 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>gk3</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>judge</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>gk-03</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Ban Giám khảo 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>doi01</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>doi-01</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Đội Sao Vàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>doi02</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>doi-02</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Đội Hồng Hà</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>doi03</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>doi-03</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Đội Cửu Long</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>doi04</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>doi-04</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Đội Trường Sơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>doi05</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>doi-05</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Đội Đông Đô</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>doi06</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>doi-06</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Đội Lam Sơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>doi07</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>doi-07</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Đội Bạch Đằng</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>doi08</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>doi-08</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Đội Thăng Long</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>doi09</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>doi-09</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Đội Phù Đổng</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>doi10</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>doi-10</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Đội Vạn Xuân</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>doi11</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>doi-11</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Đội Đại Việt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>doi12</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>122345678910</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>doi-12</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Đội Âu Lạc</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3240,118 +3753,94 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>password_host_sha256</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr"/>
+          <t>theme_mode</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>password_judge_sha256</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr"/>
+          <t>bg_color</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>#F5F4ED</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>password_team_sha256</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr"/>
+          <t>surface_color</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>#FAF9F5</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>theme_mode</t>
+          <t>text_color</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>#141413</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>bg_color</t>
+          <t>muted_color</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>#F5F4ED</t>
+          <t>#6B6960</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>surface_color</t>
+          <t>accent_color</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>#FAF9F5</t>
+          <t>#D97757</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>text_color</t>
+          <t>accent_dark_color</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>#141413</t>
+          <t>#C6613F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>muted_color</t>
+          <t>border_color</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>#6B6960</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>accent_color</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>#D97757</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>accent_dark_color</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>#C6613F</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>border_color</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>#E3E0D3</t>
         </is>
